--- a/docs/稀有枪械榜.xlsx
+++ b/docs/稀有枪械榜.xlsx
@@ -12422,7 +12422,7 @@
       <c r="V3" s="5" t="n"/>
       <c r="W3" s="8" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X3" s="7" t="inlineStr">
@@ -12619,7 +12619,7 @@
       <c r="D7" s="5" t="n"/>
       <c r="E7" s="14" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F7" s="7" t="inlineStr">
@@ -12687,7 +12687,7 @@
       <c r="AB7" s="5" t="n"/>
       <c r="AC7" s="21" t="inlineStr">
         <is>
-          <t>D+</t>
+          <t>D</t>
         </is>
       </c>
       <c r="AD7" s="7" t="inlineStr">
@@ -12884,7 +12884,7 @@
       <c r="J11" s="5" t="n"/>
       <c r="K11" s="19" t="inlineStr">
         <is>
-          <t>F+</t>
+          <t>F</t>
         </is>
       </c>
       <c r="L11" s="7" t="inlineStr">
@@ -12901,7 +12901,7 @@
       <c r="P11" s="5" t="n"/>
       <c r="Q11" s="19" t="inlineStr">
         <is>
-          <t>F+</t>
+          <t>F</t>
         </is>
       </c>
       <c r="R11" s="7" t="inlineStr">
@@ -13064,7 +13064,7 @@
       <c r="D15" s="5" t="n"/>
       <c r="E15" s="6" t="inlineStr">
         <is>
-          <t>S+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="F15" s="7" t="inlineStr">
@@ -13115,7 +13115,7 @@
       <c r="V15" s="5" t="n"/>
       <c r="W15" s="8" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X15" s="7" t="inlineStr">
@@ -13132,7 +13132,7 @@
       <c r="AB15" s="5" t="n"/>
       <c r="AC15" s="8" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>A</t>
         </is>
       </c>
       <c r="AD15" s="7" t="inlineStr">
@@ -13312,7 +13312,7 @@
       <c r="D19" s="5" t="n"/>
       <c r="E19" s="14" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F19" s="7" t="inlineStr">
@@ -13453,7 +13453,7 @@
       <c r="D23" s="5" t="n"/>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>S+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="F23" s="7" t="inlineStr">
@@ -13718,7 +13718,7 @@
       <c r="J27" s="5" t="n"/>
       <c r="K27" s="8" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>A</t>
         </is>
       </c>
       <c r="L27" s="7" t="inlineStr">
@@ -13752,7 +13752,7 @@
       <c r="V27" s="5" t="n"/>
       <c r="W27" s="14" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X27" s="7" t="inlineStr">
@@ -14000,7 +14000,7 @@
       <c r="V31" s="5" t="n"/>
       <c r="W31" s="19" t="inlineStr">
         <is>
-          <t>F+</t>
+          <t>F</t>
         </is>
       </c>
       <c r="X31" s="7" t="inlineStr">
@@ -14439,7 +14439,7 @@
       <c r="J39" s="5" t="n"/>
       <c r="K39" s="14" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>B</t>
         </is>
       </c>
       <c r="L39" s="7" t="inlineStr">
@@ -14490,7 +14490,7 @@
       <c r="AB39" s="5" t="n"/>
       <c r="AC39" s="15" t="inlineStr">
         <is>
-          <t>C+</t>
+          <t>C</t>
         </is>
       </c>
       <c r="AD39" s="7" t="inlineStr">
